--- a/firmware/Izmervania_v3.xlsx
+++ b/firmware/Izmervania_v3.xlsx
@@ -378,9 +378,19 @@
         <t>VCC_FULL_SCALE_V в Slave.ino (калибриран от Вас с мултиметър).</t>
       </text>
     </comment>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <t>Номинална стойност по данни на дипломанта (R1 = 47 kΩ). Ако резисторите се измерят с омметър, заменете с измереното.</t>
+      </text>
+    </comment>
     <comment ref="E8" authorId="0" shapeId="0">
       <text>
         <t>VCC_RELAY_ERR_V в Slave.ino (калибриран от Вас с мултиметър).</t>
+      </text>
+    </comment>
+    <comment ref="J8" authorId="0" shapeId="0">
+      <text>
+        <t>Номинална стойност по данни на дипломанта (R2 = 20 kΩ). Ако резисторите се измерят с омметър, заменете с измереното.</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -403,6 +413,11 @@
     <author>Шаблон</author>
   </authors>
   <commentList>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Номинално: модулът се захранва от извода 3V3 на NodeMCU (по данни на дипломанта). Измерената стойност може да се впише тук.</t>
+      </text>
+    </comment>
     <comment ref="E19" authorId="0" shapeId="0">
       <text>
         <t>задействания</t>
@@ -2939,7 +2954,9 @@
       </c>
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="10" t="n"/>
-      <c r="J7" s="20" t="n"/>
+      <c r="J7" s="20" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -2960,7 +2977,9 @@
       </c>
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="10" t="n"/>
-      <c r="J8" s="20" t="n"/>
+      <c r="J8" s="20" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -4296,7 +4315,9 @@
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="10" t="n"/>
-      <c r="E5" s="20" t="n"/>
+      <c r="E5" s="20" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
